--- a/artfynd/A 2203-2022 artfynd.xlsx
+++ b/artfynd/A 2203-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2203-2022 artfynd.xlsx
+++ b/artfynd/A 2203-2022 artfynd.xlsx
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100446132</v>
+        <v>100445952</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>St.Rösjön o, Srm</t>
+          <t>ST.Rösjön 100m o, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586097.5467503439</v>
+        <v>586219</v>
       </c>
       <c r="R2" t="n">
-        <v>6555097.450825643</v>
+        <v>6555078</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +755,9 @@
           <t>2022-05-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,11 +773,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,47 +790,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100445952</v>
+        <v>100446132</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -858,14 +833,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ST.Rösjön 100m o, Srm</t>
+          <t>St.Rösjön o, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586218.3503281104</v>
+        <v>586097</v>
       </c>
       <c r="R3" t="n">
-        <v>6555078.095877349</v>
+        <v>6555097</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,19 +870,9 @@
           <t>2022-05-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,6 +888,11 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -943,12 +913,7 @@
         <v>100445993</v>
       </c>
       <c r="B4" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586218.3503281104</v>
+        <v>586219</v>
       </c>
       <c r="R4" t="n">
-        <v>6555078.095877349</v>
+        <v>6555078</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,19 +978,9 @@
           <t>2022-05-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 2203-2022 artfynd.xlsx
+++ b/artfynd/A 2203-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100445952</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100446132</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,8 +1025,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100445993</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>